--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_biobio_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_biobio_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:13</t>
+    <t xml:space="preserve">2026-09-29 14:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_biobio_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_biobio_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:11</t>
+    <t xml:space="preserve">2026-09-29 18:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,7 +490,7 @@
         <v>0.73</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>39.59</v>
+        <v>39.58</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>38.85</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_biobio_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_biobio_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:41</t>
+    <t xml:space="preserve">2026-10-05 04:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,10 +490,10 @@
         <v>0.73</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>39.58</v>
+        <v>39.59</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>38.85</v>
+        <v>38.86</v>
       </c>
     </row>
     <row r="3">
@@ -504,7 +504,7 @@
         <v>-1.98</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>39.66</v>
+        <v>39.67</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>41.65</v>
